--- a/assignment3/data/trainingdataset_ontario_budgets_v14_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v14_llm_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saramurphy/Documents/GitHub/text-analysis-public-university-llm/assignment3/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088C9D23-BE91-3B46-8928-8671D3611C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210458C8-5524-5848-87EE-8311F71CE8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6620" yWindow="540" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="20000" yWindow="4300" windowWidth="17900" windowHeight="15980" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4000,13 +4000,16 @@
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="7" width="15" style="13" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="11" width="16.5" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
     <col min="13" max="14" width="19" customWidth="1"/>
     <col min="15" max="15" width="12.5" customWidth="1"/>
     <col min="16" max="16" width="12.1640625" customWidth="1"/>
     <col min="17" max="17" width="12.5" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20">
